--- a/04_Test Cases/HomePage_Test_Cases.xlsx
+++ b/04_Test Cases/HomePage_Test_Cases.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>08-03-2026</t>
+          <t>03-03-2026</t>
         </is>
       </c>
     </row>
